--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135799893</v>
       </c>
       <c r="B2" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135800380</v>
       </c>
       <c r="B3" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135800488</v>
       </c>
       <c r="B4" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>135798135</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>135800139</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>135800891</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>135800974</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>135801060</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135801344</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135801089</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135801231</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>135799947</v>
       </c>
       <c r="B13" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135800010</v>
       </c>
       <c r="B14" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>135800082</v>
       </c>
       <c r="B15" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>135800235</v>
       </c>
       <c r="B16" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135800328</v>
       </c>
       <c r="B17" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135800436</v>
       </c>
       <c r="B18" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135800711</v>
       </c>
       <c r="B19" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>135801509</v>
       </c>
       <c r="B20" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135800773</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135799893</v>
       </c>
       <c r="B2" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135800380</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135800488</v>
       </c>
       <c r="B4" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>135798135</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>135800139</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>135800891</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>135800974</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>135801060</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135801344</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135801089</v>
       </c>
       <c r="B11" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135801231</v>
       </c>
       <c r="B12" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>135799947</v>
       </c>
       <c r="B13" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135800010</v>
       </c>
       <c r="B14" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>135800082</v>
       </c>
       <c r="B15" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>135800235</v>
       </c>
       <c r="B16" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135800328</v>
       </c>
       <c r="B17" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135800436</v>
       </c>
       <c r="B18" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135800711</v>
       </c>
       <c r="B19" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>135801509</v>
       </c>
       <c r="B20" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135799893</v>
       </c>
       <c r="B2" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135800380</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135800488</v>
       </c>
       <c r="B4" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>135798135</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>135800139</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>135800891</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>135800974</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>135801060</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135801344</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135801089</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135801231</v>
       </c>
       <c r="B12" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>135799947</v>
       </c>
       <c r="B13" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135800010</v>
       </c>
       <c r="B14" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>135800082</v>
       </c>
       <c r="B15" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>135800235</v>
       </c>
       <c r="B16" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135800328</v>
       </c>
       <c r="B17" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135800436</v>
       </c>
       <c r="B18" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135800711</v>
       </c>
       <c r="B19" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>135801509</v>
       </c>
       <c r="B20" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135800773</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135799893</v>
       </c>
       <c r="B2" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135800380</v>
       </c>
       <c r="B3" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135800488</v>
       </c>
       <c r="B4" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>135798135</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>135800139</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>135800891</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>135800974</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>135801060</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135801344</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135801089</v>
       </c>
       <c r="B11" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135801231</v>
       </c>
       <c r="B12" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>135799947</v>
       </c>
       <c r="B13" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135800010</v>
       </c>
       <c r="B14" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>135800082</v>
       </c>
       <c r="B15" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>135800235</v>
       </c>
       <c r="B16" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135800328</v>
       </c>
       <c r="B17" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135800436</v>
       </c>
       <c r="B18" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135800711</v>
       </c>
       <c r="B19" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>135801509</v>
       </c>
       <c r="B20" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135800773</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135799893</v>
       </c>
       <c r="B2" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135800380</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135800488</v>
       </c>
       <c r="B4" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>135798135</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>135800139</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>135800891</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>135800974</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>135801060</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135801344</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135801089</v>
       </c>
       <c r="B11" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135801231</v>
       </c>
       <c r="B12" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>135799947</v>
       </c>
       <c r="B13" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135800010</v>
       </c>
       <c r="B14" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>135800082</v>
       </c>
       <c r="B15" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>135800235</v>
       </c>
       <c r="B16" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135800328</v>
       </c>
       <c r="B17" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135800436</v>
       </c>
       <c r="B18" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135800711</v>
       </c>
       <c r="B19" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>135801509</v>
       </c>
       <c r="B20" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135800773</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135799893</v>
       </c>
       <c r="B2" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135800380</v>
       </c>
       <c r="B3" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135800488</v>
       </c>
       <c r="B4" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>135798135</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>135800139</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>135800891</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>135800974</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>135801060</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135801344</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135801089</v>
       </c>
       <c r="B11" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135801231</v>
       </c>
       <c r="B12" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>135799947</v>
       </c>
       <c r="B13" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135800010</v>
       </c>
       <c r="B14" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>135800082</v>
       </c>
       <c r="B15" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>135800235</v>
       </c>
       <c r="B16" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135800328</v>
       </c>
       <c r="B17" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135800436</v>
       </c>
       <c r="B18" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135800711</v>
       </c>
       <c r="B19" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>135801509</v>
       </c>
       <c r="B20" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135799893</v>
       </c>
       <c r="B2" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135800380</v>
       </c>
       <c r="B3" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135800488</v>
       </c>
       <c r="B4" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>135798135</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>135800139</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>135800891</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>135800974</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>135801060</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135801344</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135801089</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135801231</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>135799947</v>
       </c>
       <c r="B13" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135800010</v>
       </c>
       <c r="B14" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>135800082</v>
       </c>
       <c r="B15" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>135800235</v>
       </c>
       <c r="B16" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135800328</v>
       </c>
       <c r="B17" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>135800436</v>
       </c>
       <c r="B18" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135800711</v>
       </c>
       <c r="B19" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>135801509</v>
       </c>
       <c r="B20" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135800773</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56288-2025 artfynd.xlsx
+++ b/artfynd/A 56288-2025 artfynd.xlsx
@@ -3108,7 +3108,7 @@
         <v>135801549</v>
       </c>
       <c r="B22" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
